--- a/week3/auto_output/auto_excel/301563_云汉芯城_auto.xlsx
+++ b/week3/auto_output/auto_excel/301563_云汉芯城_auto.xlsx
@@ -1,14 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_交叉校验" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_股权转让" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6877,4 +6879,512 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>校验类型</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>批次/时点</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>认购方数量</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>合计金额(万元)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>合计股数(万股)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>有限公司设立</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>有限公司第一次增资</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>有限公司第二次增资（A轮第一批）</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>有限公司第三次增资（A轮第二批）</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>有限公司第四次增资（资本公积转增）</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1863</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>有限公司第五次增资（B轮）</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>158.32</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>股份公司第一次增资（C轮-外部投资人）</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>515</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>股份公司第一次增资（C轮-员工股权激励）</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>股份公司第二次增资（D轮）</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>股份公司第三次增资（D+轮）</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>135.66</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>股东持股加总</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>t0/整体变更设立股份公司（2015-12-03）</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>股东持股加总</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2018年4月第一次股权转让后</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>股东持股加总</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2018年7月C轮增资及第二次股权转让后</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>4635</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>4635</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>股东持股加总</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2019年8月第三次股权转让后</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>4635</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>4635</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>股东持股加总</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2020年5月D轮增资后</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>4748.05</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>4748.05</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>股东持股加总</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2020年9月D+轮增资及第四次股权转让后（IPO前最终结构）</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>4883.71</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>4883.71</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PDF页码</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>转让日期</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>转让方</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>受让方</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>转让数量(万股)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>转让价格(元/股)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>转让金额(万元)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>原文证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>自动化提取暂不支持股权转让Sheet，此Sheet需人工补全。Gold标准中已包含。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>